--- a/public/inputs/y07-portuguese-1st - input.xlsx
+++ b/public/inputs/y07-portuguese-1st - input.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unidade 1 · TEXTOS DOS MEDIA</t>
+          <t>Unidade 1 · Textos dos Media</t>
         </is>
       </c>
     </row>
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unidade 2 · UMA VIAGEM</t>
+          <t>Unidade 2 · Uma Viagem</t>
         </is>
       </c>
     </row>
@@ -465,7 +465,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unidade 3 · O PALCO À ESPERA</t>
+          <t>Unidade 3 · O Palco à Espera</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unidade 4 · A PALAVRA EM MÚSICA</t>
+          <t>Unidade 4 · A Palavra em Música</t>
         </is>
       </c>
     </row>
